--- a/examples/STUDY01_TRAIL01/outputs/feedback/SDTM/SDTM_ganesh.xlsx
+++ b/examples/STUDY01_TRAIL01/outputs/feedback/SDTM/SDTM_ganesh.xlsx
@@ -15,12 +15,15 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Details" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Details!$A$3:$J$285</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="336">
   <si>
     <t>pyCoreGage Report — SDTM</t>
   </si>
@@ -1016,6 +1019,18 @@
   </si>
   <si>
     <t>HITTT</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>star</t>
+  </si>
+  <si>
+    <t>warrier</t>
+  </si>
+  <si>
+    <t>god</t>
   </si>
 </sst>
 </file>
@@ -1696,12 +1711,18 @@
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>35</v>
+        <v>332</v>
       </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
